--- a/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D79A2081-96C1-4A2D-82DB-F57BD2476D13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FAF2D7A-9D43-47AD-9FCC-799F52C8A055}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F838D61-26C2-411F-B1BC-C73BC3A0AA62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4402B266-77AE-4D17-8839-B3A413311173}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B607BEB-FAD9-4E17-A613-9693764594D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBDE4C33-C307-451F-A317-27CB877F553F}"/>
 </file>